--- a/data/output/workbook/2026-06-30.xlsx
+++ b/data/output/workbook/2026-06-30.xlsx
@@ -371,7 +371,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="9429750"/>
+    <ext cx="10125075" cy="9229725"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -401,7 +401,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="9467850"/>
+    <ext cx="10125075" cy="9086850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -431,7 +431,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="9172575"/>
+    <ext cx="10125075" cy="9696450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30 04:32</t>
+          <t>2026-06-30 07:45</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:Q76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1175,899 +1175,899 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="29" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="29" t="inlineStr">
         <is>
           <t>Pittsburgh Pirates offense vs Philadelphia Phillies defense</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="30" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B60" s="30" t="inlineStr">
+      <c r="B63" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C60" s="30" t="inlineStr">
+      <c r="C63" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D60" s="30" t="inlineStr">
+      <c r="D63" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E60" s="30" t="inlineStr">
+      <c r="E63" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F60" s="30" t="inlineStr">
+      <c r="F63" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G60" s="30" t="inlineStr">
+      <c r="G63" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H60" s="30" t="inlineStr">
+      <c r="H63" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I60" s="30" t="inlineStr">
+      <c r="I63" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J60" s="30" t="inlineStr">
+      <c r="J63" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K60" s="30" t="inlineStr">
+      <c r="K63" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L60" s="30" t="inlineStr">
+      <c r="L63" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M60" s="30" t="inlineStr">
+      <c r="M63" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N60" s="30" t="inlineStr">
+      <c r="N63" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O60" s="30" t="inlineStr">
+      <c r="O63" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P60" s="30" t="inlineStr">
+      <c r="P63" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q60" s="30" t="inlineStr">
+      <c r="Q63" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B61" s="32" t="n">
-        <v>5.104</v>
-      </c>
-      <c r="C61" s="32" t="n">
-        <v>5.667</v>
-      </c>
-      <c r="D61" s="32" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="E61" s="32" t="n">
-        <v>5.733</v>
-      </c>
-      <c r="F61" s="32" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="G61" s="32" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="H61" s="33" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="I61" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J61" s="34" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="K61" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L61" s="32" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M61" s="32" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="N61" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O61" s="32" t="n">
-        <v>4.567</v>
-      </c>
-      <c r="P61" s="32" t="n">
-        <v>4.827</v>
-      </c>
-      <c r="Q61" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B62" s="32" t="n">
-        <v>8.811999999999999</v>
-      </c>
-      <c r="C62" s="32" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="D62" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E62" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F62" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G62" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H62" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I62" s="32" t="inlineStr"/>
-      <c r="J62" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K62" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L62" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M62" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N62" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O62" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="P62" s="32" t="n">
-        <v>9.319000000000001</v>
-      </c>
-      <c r="Q62" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B63" s="32" t="n">
-        <v>1.188</v>
-      </c>
-      <c r="C63" s="32" t="n">
-        <v>2.167</v>
-      </c>
-      <c r="D63" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E63" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F63" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G63" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H63" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I63" s="32" t="inlineStr"/>
-      <c r="J63" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K63" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L63" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M63" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N63" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O63" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P63" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q63" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B64" s="32" t="n">
-        <v>9.708</v>
+        <v>5.104</v>
       </c>
       <c r="C64" s="32" t="n">
-        <v>9.167</v>
-      </c>
-      <c r="D64" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E64" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F64" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G64" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H64" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I64" s="32" t="inlineStr"/>
-      <c r="J64" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K64" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L64" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M64" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N64" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5.667</v>
+      </c>
+      <c r="D64" s="32" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="E64" s="32" t="n">
+        <v>5.733</v>
+      </c>
+      <c r="F64" s="32" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="G64" s="32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H64" s="33" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="I64" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J64" s="34" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="K64" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L64" s="32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M64" s="32" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="N64" s="32" t="n">
+        <v>4.8</v>
       </c>
       <c r="O64" s="32" t="n">
-        <v>8.800000000000001</v>
+        <v>4.567</v>
       </c>
       <c r="P64" s="32" t="n">
-        <v>9.276999999999999</v>
+        <v>4.827</v>
       </c>
       <c r="Q64" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="31" t="inlineStr">
         <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B65" s="32" t="n">
+        <v>8.811999999999999</v>
+      </c>
+      <c r="C65" s="32" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H65" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I65" s="32" t="inlineStr"/>
+      <c r="J65" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O65" s="32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="P65" s="32" t="n">
+        <v>9.319000000000001</v>
+      </c>
+      <c r="Q65" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B66" s="32" t="n">
+        <v>1.188</v>
+      </c>
+      <c r="C66" s="32" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="D66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H66" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I66" s="32" t="inlineStr"/>
+      <c r="J66" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q66" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B67" s="32" t="n">
+        <v>9.708</v>
+      </c>
+      <c r="C67" s="32" t="n">
+        <v>9.167</v>
+      </c>
+      <c r="D67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H67" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I67" s="32" t="inlineStr"/>
+      <c r="J67" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O67" s="32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="P67" s="32" t="n">
+        <v>9.276999999999999</v>
+      </c>
+      <c r="Q67" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B65" s="32" t="n">
+      <c r="B68" s="32" t="n">
         <v>0.569</v>
       </c>
-      <c r="C65" s="32" t="n">
+      <c r="C68" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="D65" s="32" t="n">
+      <c r="D68" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="E65" s="32" t="n">
+      <c r="E68" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="F65" s="32" t="n">
+      <c r="F68" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="G65" s="32" t="n">
+      <c r="G68" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="H65" s="36" t="inlineStr">
+      <c r="H68" s="36" t="inlineStr">
         <is>
           <t>13th</t>
         </is>
       </c>
-      <c r="I65" s="32" t="inlineStr">
+      <c r="I68" s="32" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J65" s="34" t="inlineStr">
+      <c r="J68" s="34" t="inlineStr">
         <is>
           <t>25th</t>
         </is>
       </c>
-      <c r="K65" s="32" t="n">
+      <c r="K68" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="L65" s="32" t="n">
+      <c r="L68" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="M65" s="32" t="n">
+      <c r="M68" s="32" t="n">
         <v>0.733</v>
       </c>
-      <c r="N65" s="32" t="n">
+      <c r="N68" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="O65" s="32" t="n">
+      <c r="O68" s="32" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="P65" s="32" t="n">
+      <c r="P68" s="32" t="n">
         <v>0.542</v>
       </c>
-      <c r="Q65" s="35" t="inlineStr">
+      <c r="Q68" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="29" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="29" t="inlineStr">
         <is>
           <t>Philadelphia Phillies offense vs Pittsburgh Pirates defense</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="30" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B68" s="30" t="inlineStr">
+      <c r="B71" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C68" s="30" t="inlineStr">
+      <c r="C71" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D68" s="30" t="inlineStr">
+      <c r="D71" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E68" s="30" t="inlineStr">
+      <c r="E71" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F68" s="30" t="inlineStr">
+      <c r="F71" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G68" s="30" t="inlineStr">
+      <c r="G71" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H68" s="30" t="inlineStr">
+      <c r="H71" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I68" s="30" t="inlineStr">
+      <c r="I71" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J68" s="30" t="inlineStr">
+      <c r="J71" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K68" s="30" t="inlineStr">
+      <c r="K71" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L68" s="30" t="inlineStr">
+      <c r="L71" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M68" s="30" t="inlineStr">
+      <c r="M71" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N68" s="30" t="inlineStr">
+      <c r="N71" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O68" s="30" t="inlineStr">
+      <c r="O71" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P68" s="30" t="inlineStr">
+      <c r="P71" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q68" s="30" t="inlineStr">
+      <c r="Q71" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="n">
-        <v>4.507</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>5.167</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="E69" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="F69" s="32" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G69" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H69" s="33" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J69" s="34" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L69" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="M69" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N69" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>5.733</v>
-      </c>
-      <c r="P69" s="32" t="n">
-        <v>4.701</v>
-      </c>
-      <c r="Q69" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B70" s="32" t="n">
-        <v>7.234</v>
-      </c>
-      <c r="C70" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="D70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O70" s="32" t="n">
-        <v>9.333</v>
-      </c>
-      <c r="P70" s="32" t="n">
-        <v>7.792</v>
-      </c>
-      <c r="Q70" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B71" s="32" t="n">
-        <v>1.213</v>
-      </c>
-      <c r="C71" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q71" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>8.426</v>
+        <v>4.507</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="D72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5.167</v>
+      </c>
+      <c r="D72" s="32" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="E72" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="F72" s="32" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G72" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H72" s="33" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J72" s="34" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L72" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M72" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N72" s="32" t="n">
+        <v>5.4</v>
       </c>
       <c r="O72" s="32" t="n">
-        <v>11.5</v>
+        <v>5.733</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>9.292</v>
+        <v>4.701</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="n">
+        <v>7.234</v>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>9.333</v>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>7.792</v>
+      </c>
+      <c r="Q73" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B74" s="32" t="n">
+        <v>1.213</v>
+      </c>
+      <c r="C74" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q74" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B75" s="32" t="n">
+        <v>8.426</v>
+      </c>
+      <c r="C75" s="32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="D75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H75" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I75" s="32" t="inlineStr"/>
+      <c r="J75" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O75" s="32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="P75" s="32" t="n">
+        <v>9.292</v>
+      </c>
+      <c r="Q75" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B73" s="32" t="n">
+      <c r="B76" s="32" t="n">
         <v>0.597</v>
       </c>
-      <c r="C73" s="32" t="n">
+      <c r="C76" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="D73" s="32" t="n">
+      <c r="D76" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="E73" s="32" t="n">
+      <c r="E76" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="F73" s="32" t="n">
+      <c r="F76" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="G73" s="32" t="n">
+      <c r="G76" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="H73" s="33" t="inlineStr">
+      <c r="H76" s="33" t="inlineStr">
         <is>
           <t>5th</t>
         </is>
       </c>
-      <c r="I73" s="32" t="inlineStr">
+      <c r="I76" s="32" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J73" s="34" t="inlineStr">
+      <c r="J76" s="34" t="inlineStr">
         <is>
           <t>24th</t>
         </is>
       </c>
-      <c r="K73" s="32" t="n">
+      <c r="K76" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="L73" s="32" t="n">
+      <c r="L76" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="M73" s="32" t="n">
+      <c r="M76" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="N73" s="32" t="n">
+      <c r="N76" s="32" t="n">
         <v>0.45</v>
       </c>
-      <c r="O73" s="32" t="n">
+      <c r="O76" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="P73" s="32" t="n">
+      <c r="P76" s="32" t="n">
         <v>0.417</v>
       </c>
-      <c r="Q73" s="35" t="inlineStr">
+      <c r="Q76" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7602,7 +7602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:Q73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7619,170 +7619,324 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="29" t="inlineStr">
+        <is>
+          <t>San Diego Padres offense vs Chicago Cubs defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B60" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C60" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D60" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E60" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F60" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G60" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H60" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I60" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J60" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K60" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L60" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M60" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N60" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O60" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P60" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q60" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="61">
-      <c r="A61" s="29" t="inlineStr">
-        <is>
-          <t>San Diego Padres offense vs Chicago Cubs defense</t>
+      <c r="A61" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B61" s="32" t="n">
+        <v>3.987</v>
+      </c>
+      <c r="C61" s="32" t="n">
+        <v>3.733</v>
+      </c>
+      <c r="D61" s="32" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E61" s="32" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="F61" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G61" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H61" s="36" t="inlineStr">
+        <is>
+          <t>19th</t>
+        </is>
+      </c>
+      <c r="I61" s="32" t="inlineStr"/>
+      <c r="J61" s="33" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="K61" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L61" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="M61" s="32" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="N61" s="32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O61" s="32" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="P61" s="32" t="n">
+        <v>4.644</v>
+      </c>
+      <c r="Q61" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B62" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C62" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D62" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E62" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F62" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G62" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H62" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I62" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J62" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K62" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L62" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M62" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N62" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O62" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P62" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q62" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A62" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B62" s="32" t="n">
+        <v>7.087</v>
+      </c>
+      <c r="C62" s="32" t="n">
+        <v>6.833</v>
+      </c>
+      <c r="D62" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E62" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F62" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G62" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H62" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I62" s="32" t="inlineStr"/>
+      <c r="J62" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K62" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L62" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M62" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N62" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O62" s="32" t="n">
+        <v>6.833</v>
+      </c>
+      <c r="P62" s="32" t="n">
+        <v>7.896</v>
+      </c>
+      <c r="Q62" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B63" s="32" t="n">
-        <v>3.987</v>
+        <v>1.022</v>
       </c>
       <c r="C63" s="32" t="n">
-        <v>3.733</v>
-      </c>
-      <c r="D63" s="32" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="E63" s="32" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="F63" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G63" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H63" s="36" t="inlineStr">
-        <is>
-          <t>19th</t>
+        <v>1.333</v>
+      </c>
+      <c r="D63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H63" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I63" s="32" t="inlineStr"/>
-      <c r="J63" s="33" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-      <c r="K63" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L63" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="M63" s="32" t="n">
-        <v>4.067</v>
-      </c>
-      <c r="N63" s="32" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O63" s="32" t="n">
-        <v>4.267</v>
-      </c>
-      <c r="P63" s="32" t="n">
-        <v>4.644</v>
+      <c r="J63" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q63" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B64" s="32" t="n">
-        <v>7.087</v>
+        <v>8.348000000000001</v>
       </c>
       <c r="C64" s="32" t="n">
-        <v>6.833</v>
+        <v>9.333</v>
       </c>
       <c r="D64" s="32" t="inlineStr">
         <is>
@@ -7836,398 +7990,398 @@
         </is>
       </c>
       <c r="O64" s="32" t="n">
-        <v>6.833</v>
+        <v>7</v>
       </c>
       <c r="P64" s="32" t="n">
-        <v>7.896</v>
+        <v>7.708</v>
       </c>
       <c r="Q64" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B65" s="32" t="n">
-        <v>1.022</v>
+        <v>0.329</v>
       </c>
       <c r="C65" s="32" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="D65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H65" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.433</v>
+      </c>
+      <c r="D65" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E65" s="32" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="F65" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G65" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="34" t="inlineStr">
+        <is>
+          <t>27th</t>
         </is>
       </c>
       <c r="I65" s="32" t="inlineStr"/>
-      <c r="J65" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J65" s="36" t="inlineStr">
+        <is>
+          <t>14th</t>
+        </is>
+      </c>
+      <c r="K65" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L65" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M65" s="32" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="N65" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O65" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P65" s="32" t="n">
+        <v>0.444</v>
       </c>
       <c r="Q65" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B66" s="32" t="n">
-        <v>8.348000000000001</v>
-      </c>
-      <c r="C66" s="32" t="n">
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Chicago Cubs offense vs San Diego Padres defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>5.027</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>5.367</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>6.267</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H69" s="36" t="inlineStr">
+        <is>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J69" s="34" t="inlineStr">
+        <is>
+          <t>21st</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="Q69" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>8.438000000000001</v>
+      </c>
+      <c r="C70" s="32" t="n">
         <v>9.333</v>
       </c>
-      <c r="D66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H66" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I66" s="32" t="inlineStr"/>
-      <c r="J66" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O66" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="P66" s="32" t="n">
-        <v>7.708</v>
-      </c>
-      <c r="Q66" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B67" s="32" t="n">
-        <v>0.329</v>
-      </c>
-      <c r="C67" s="32" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="D67" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E67" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="F67" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G67" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" s="34" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="I67" s="32" t="inlineStr"/>
-      <c r="J67" s="36" t="inlineStr">
-        <is>
-          <t>14th</t>
-        </is>
-      </c>
-      <c r="K67" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L67" s="32" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M67" s="32" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="N67" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O67" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="P67" s="32" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="Q67" s="35" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>Chicago Cubs offense vs San Diego Padres defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>8.333</v>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>7.848</v>
+      </c>
+      <c r="Q70" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>5.027</v>
+        <v>1.104</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>5.367</v>
-      </c>
-      <c r="D71" s="32" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="E71" s="32" t="n">
-        <v>6.267</v>
-      </c>
-      <c r="F71" s="32" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="G71" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H71" s="36" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J71" s="34" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="L71" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="M71" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="N71" s="32" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="O71" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="P71" s="32" t="n">
-        <v>3.87</v>
+        <v>1</v>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr"/>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>8.438000000000001</v>
+        <v>8.458</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>9.333</v>
+        <v>8.833</v>
       </c>
       <c r="D72" s="32" t="inlineStr">
         <is>
@@ -8281,225 +8435,71 @@
         </is>
       </c>
       <c r="O72" s="32" t="n">
-        <v>8.333</v>
+        <v>4.833</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>7.848</v>
+        <v>8.304</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>1.104</v>
+        <v>0.417</v>
       </c>
       <c r="C73" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.533</v>
+      </c>
+      <c r="D73" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E73" s="32" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="F73" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="34" t="inlineStr">
+        <is>
+          <t>29th</t>
         </is>
       </c>
       <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J73" s="33" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>0.457</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>8.458</v>
-      </c>
-      <c r="C74" s="32" t="n">
-        <v>8.833</v>
-      </c>
-      <c r="D74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="32" t="n">
-        <v>4.833</v>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>8.304</v>
-      </c>
-      <c r="Q74" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>0.417</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="D75" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E75" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="F75" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="34" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="33" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M75" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="N75" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>0.457</v>
-      </c>
-      <c r="Q75" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8596,7 +8596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8740,13 +8740,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.3444193548387097</v>
+        <v>0.3364086687306502</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -8770,7 +8770,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 34.4% (fair +190). Your call.</t>
+          <t>Model 33.6% (fair +197). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -8787,12 +8787,12 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Houston Astros</t>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -8802,17 +8802,17 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.4990610328638498</v>
+        <v>0.4422131147540984</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +100). Your call.</t>
+          <t>Model 44.2% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8848,37 +8848,37 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Atlanta Braves</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.4461764705882353</v>
+        <v>0.5517878048780488</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>124</v>
+        <v>-123</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>138</v>
+        <v>-105</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 44.6% (fair +124). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -8919,12 +8919,12 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>Minnesota Twins @ Houston Astros</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -8934,17 +8934,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.465726872246696</v>
+        <v>0.4990610328638498</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 49.9% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -8985,12 +8985,12 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -9000,14 +9000,14 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.4636563876651982</v>
+        <v>0.465726872246696</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>127</v>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 46.4% (fair +116). Your call.</t>
+          <t>Model 46.6% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9051,12 +9051,12 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -9066,17 +9066,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5734116591928251</v>
+        <v>0.4781447963800905</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-134</v>
+        <v>109</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-123</v>
+        <v>121</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -9100,7 +9100,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 57.3% (fair -134). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9117,32 +9117,32 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.487887323943662</v>
+        <v>0.5112745098039215</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>105</v>
+        <v>-105</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9166,7 +9166,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 51.1% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9178,17 +9178,17 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -9198,17 +9198,17 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4987980769230769</v>
+        <v>0.5728504504504505</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>100</v>
+        <v>-134</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>108</v>
+        <v>-122</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +100). Your call.</t>
+          <t>Model 57.3% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9249,32 +9249,32 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Baltimore Orioles</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4559911894273127</v>
+        <v>0.5245930693069306</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>119</v>
+        <v>-110</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>127</v>
+        <v>-102</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9298,7 +9298,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 45.6% (fair +119). Your call.</t>
+          <t>Model 52.5% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9310,37 +9310,37 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Toronto Blue Jays</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Milwaukee Brewers -1.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5072549019607843</v>
+        <v>0.4612000000000001</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-103</v>
+        <v>117</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9364,7 +9364,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 50.7% (fair -103). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9376,17 +9376,17 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Atlanta Braves</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -9396,17 +9396,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4236065573770492</v>
+        <v>0.4987980769230769</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9430,7 +9430,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 49.9% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9442,17 +9442,17 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Baltimore Orioles</t>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -9462,17 +9462,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4761290322580645</v>
+        <v>0.4249590163934426</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9496,7 +9496,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 42.5% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9513,32 +9513,32 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>Chicago White Sox @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5051470588235294</v>
+        <v>0.4559911894273127</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-102</v>
+        <v>119</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -9562,7 +9562,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 50.5% (fair -102). Your call.</t>
+          <t>Model 45.6% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9574,17 +9574,17 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>Chicago White Sox @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -9594,17 +9594,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5327307692307692</v>
+        <v>0.4761290322580645</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-114</v>
+        <v>110</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-108</v>
+        <v>117</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9628,7 +9628,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 53.3% (fair -114). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9640,17 +9640,17 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -9660,17 +9660,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4195081967213115</v>
+        <v>0.5327307692307692</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>138</v>
+        <v>-114</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>144</v>
+        <v>-108</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 42.0% (fair +138). Your call.</t>
+          <t>Model 53.3% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9706,17 +9706,17 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Toronto Blue Jays</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -9726,17 +9726,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.490576923076923</v>
+        <v>0.4195081967213115</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 49.1% (fair +104). Your call.</t>
+          <t>Model 42.0% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9769,9 +9769,75 @@
         <v/>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>New York Mets @ Toronto Blue Jays</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>23:07</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>New York Mets</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>0.4920192307692308</v>
+      </c>
+      <c r="G21" s="14" t="n">
+        <v>103</v>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>108</v>
+      </c>
+      <c r="I21" s="13">
+        <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
+        <v/>
+      </c>
+      <c r="J21" s="16">
+        <f>IF($H$21="","",$F$21*IF($H$21&lt;0,-100/$H$21,$H$21/100)-(1-$F$21))</f>
+        <v/>
+      </c>
+      <c r="K21" s="17">
+        <f>IF($H$21="","",MAX(0,($F$21*IF($H$21&lt;0,-100/$H$21,$H$21/100)-(1-$F$21))/IF($H$21&lt;0,-100/$H$21,$H$21/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L21" s="18">
+        <f>IF($H$21="","",ROUND(MIN($K$21,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M21" s="12">
+        <f>IF($J$21="","",IF($J$21&lt;0,"Pass",IF($J$21&lt;'Settings'!$B$4,"Thin",IF($J$21&lt;0.06,"✅ Sharp band",IF($J$21&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N21" s="19" t="inlineStr">
+        <is>
+          <t>Model 49.2% (fair +103). Your call.</t>
+        </is>
+      </c>
+      <c r="O21" s="15" t="n"/>
+      <c r="P21" s="16">
+        <f>IF(OR($H$21="",$O$21=""),"",(1+IF($H$21&lt;0,-100/$H$21,$H$21/100))/(1+IF($O$21&lt;0,-100/$O$21,$O$21/100))-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J20">
+  <conditionalFormatting sqref="J5:J21">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -9793,7 +9859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P96"/>
+  <dimension ref="A1:P98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10065,17 +10131,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 11</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.3929</v>
+        <v>0.5532</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>155</v>
+        <v>-124</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -10099,7 +10165,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 39.3% (fair +155). Your call.</t>
+          <t>Model 55.3% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -10131,17 +10197,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Under 11</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.6071</v>
+        <v>0.4468</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-155</v>
+        <v>124</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -10165,7 +10231,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 60.7% (fair -155). Your call.</t>
+          <t>Model 44.7% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -10207,7 +10273,7 @@
         <v>155</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -10461,17 +10527,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4777</v>
+        <v>0.5245930693069306</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>109</v>
+        <v>-110</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>111</v>
+        <v>-102</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -10495,7 +10561,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 52.5% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -10527,14 +10593,14 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5223</v>
+        <v>0.4754411764705882</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-109</v>
+        <v>110</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>104</v>
@@ -10561,7 +10627,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
+          <t>Model 47.5% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -10597,13 +10663,13 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.3444193548387097</v>
+        <v>0.3364086687306502</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -10627,7 +10693,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 34.4% (fair +190). Your call.</t>
+          <t>Model 33.6% (fair +197). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -10663,13 +10729,13 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.6555692307692307</v>
+        <v>0.6636148606811146</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-190</v>
+        <v>-197</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-212</v>
+        <v>-223</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -10693,7 +10759,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 65.6% (fair -190). Your call.</t>
+          <t>Model 66.4% (fair -197). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -10729,10 +10795,10 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5051470588235294</v>
+        <v>0.5112745098039215</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-102</v>
+        <v>-105</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>104</v>
@@ -10759,7 +10825,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 50.5% (fair -102). Your call.</t>
+          <t>Model 51.1% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -10795,13 +10861,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4948788461538461</v>
+        <v>0.48875</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-108</v>
+        <v>100</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -10825,7 +10891,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 49.5% (fair +102). Your call.</t>
+          <t>Model 48.9% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -10842,32 +10908,32 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Philadelphia Phillies -1.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4265777777777778</v>
+        <v>0.494356862745098</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>125</v>
+        <v>-104</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -10891,7 +10957,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 42.7% (fair +134). Your call.</t>
+          <t>Model 49.4% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -10908,32 +10974,32 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Pittsburgh Pirates +1.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5734116591928251</v>
+        <v>0.5056218905472637</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-134</v>
+        <v>-102</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-123</v>
+        <v>101</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -10957,7 +11023,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 57.3% (fair -134). Your call.</t>
+          <t>Model 50.6% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -10984,22 +11050,22 @@
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4906</v>
+        <v>0.4271555555555555</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -11023,7 +11089,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 49.1% (fair +104). Your call.</t>
+          <t>Model 42.7% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11050,22 +11116,22 @@
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5094000000000001</v>
+        <v>0.5728504504504505</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-104</v>
+        <v>-134</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>102</v>
+        <v>-122</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -11089,7 +11155,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -104). Your call.</t>
+          <t>Model 57.3% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11116,22 +11182,22 @@
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees -1.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4536</v>
+        <v>0.4906</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>167</v>
+        <v>115</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -11155,7 +11221,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 45.4% (fair +120). Your call.</t>
+          <t>Model 49.1% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11182,22 +11248,22 @@
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers +1.5</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5464</v>
+        <v>0.5094000000000001</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-120</v>
+        <v>-104</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-123</v>
+        <v>111</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -11221,7 +11287,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 54.6% (fair -120). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11238,32 +11304,32 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Toronto Blue Jays</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>New York Yankees -1.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.490576923076923</v>
+        <v>0.4536</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>108</v>
+        <v>167</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -11287,7 +11353,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 49.1% (fair +104). Your call.</t>
+          <t>Model 45.4% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -11304,32 +11370,32 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Toronto Blue Jays</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>Detroit Tigers +1.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5094315789473685</v>
+        <v>0.5464</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-104</v>
+        <v>-120</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-109</v>
+        <v>-126</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -11353,7 +11419,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -104). Your call.</t>
+          <t>Model 54.6% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -11380,22 +11446,22 @@
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4456</v>
+        <v>0.4920192307692308</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>-104</v>
+        <v>108</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -11419,7 +11485,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 44.6% (fair +124). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -11446,22 +11512,22 @@
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5544</v>
+        <v>0.5080173913043478</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-124</v>
+        <v>-103</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>115</v>
+        <v>-107</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -11485,7 +11551,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 55.4% (fair -124). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -11512,22 +11578,22 @@
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays -1.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.347</v>
+        <v>0.4456</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>188</v>
+        <v>124</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>186</v>
+        <v>121</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -11551,7 +11617,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 34.7% (fair +188). Your call.</t>
+          <t>Model 44.6% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -11578,22 +11644,22 @@
       </c>
       <c r="D30" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
         <is>
-          <t>New York Mets +1.5</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.653</v>
+        <v>0.5544</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>-188</v>
+        <v>-124</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>186</v>
+        <v>113</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -11617,7 +11683,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 65.3% (fair -188). Your call.</t>
+          <t>Model 55.4% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -11634,32 +11700,32 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Boston Red Sox</t>
+          <t>New York Mets @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Toronto Blue Jays -1.5</t>
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.5311</v>
+        <v>0.347</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>-113</v>
+        <v>188</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>125</v>
+        <v>186</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -11683,7 +11749,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 53.1% (fair -113). Your call.</t>
+          <t>Model 34.7% (fair +188). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -11700,32 +11766,32 @@
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Boston Red Sox</t>
+          <t>New York Mets @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>New York Mets +1.5</t>
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.4689</v>
+        <v>0.653</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>113</v>
+        <v>-188</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>127</v>
+        <v>182</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -11749,7 +11815,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 46.9% (fair +113). Your call.</t>
+          <t>Model 65.3% (fair -188). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -11776,22 +11842,22 @@
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Over 11</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.3057</v>
+        <v>0.5311</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>227</v>
+        <v>-113</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -11815,7 +11881,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 30.6% (fair +227). Your call.</t>
+          <t>Model 53.1% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -11842,22 +11908,22 @@
       </c>
       <c r="D34" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
         <is>
-          <t>Under 11</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.6942999999999999</v>
+        <v>0.4689</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-227</v>
+        <v>113</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -11881,7 +11947,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 69.4% (fair -227). Your call.</t>
+          <t>Model 46.9% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -11908,22 +11974,22 @@
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox -1.5</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.3438</v>
+        <v>0.4622</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>191</v>
+        <v>116</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>156</v>
+        <v>104</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -11947,7 +12013,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 34.4% (fair +191). Your call.</t>
+          <t>Model 46.2% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -11974,22 +12040,22 @@
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals +1.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.6562</v>
+        <v>0.5378000000000001</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>-191</v>
+        <v>-116</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>-116</v>
+        <v>117</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -12013,7 +12079,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 65.6% (fair -191). Your call.</t>
+          <t>Model 53.8% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -12030,32 +12096,32 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Atlanta Braves</t>
+          <t>Washington Nationals @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Boston Red Sox -1.5</t>
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.4236065573770492</v>
+        <v>0.3438</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>136</v>
+        <v>191</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -12079,7 +12145,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 34.4% (fair +191). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -12096,32 +12162,32 @@
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Atlanta Braves</t>
+          <t>Washington Nationals @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C38" s="20" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E38" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Washington Nationals +1.5</t>
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.5764131147540984</v>
+        <v>0.6562</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>-136</v>
+        <v>-191</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>-144</v>
+        <v>-115</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -12145,7 +12211,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 65.6% (fair -191). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -12172,22 +12238,22 @@
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Over 10</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.3333</v>
+        <v>0.4249590163934426</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>200</v>
+        <v>135</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -12211,7 +12277,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 33.3% (fair +200). Your call.</t>
+          <t>Model 42.5% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12238,22 +12304,22 @@
       </c>
       <c r="D40" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E40" s="20" t="inlineStr">
         <is>
-          <t>Under 10</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.6667000000000001</v>
+        <v>0.5749991701244813</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>-200</v>
+        <v>-135</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>-104</v>
+        <v>-141</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -12277,7 +12343,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 66.7% (fair -200). Your call.</t>
+          <t>Model 57.5% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -12304,22 +12370,22 @@
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves -1.5</t>
+          <t>Over 10</t>
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.4134</v>
+        <v>0.3333</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>142</v>
+        <v>200</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -12343,7 +12409,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 41.3% (fair +142). Your call.</t>
+          <t>Model 33.3% (fair +200). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -12370,22 +12436,22 @@
       </c>
       <c r="D42" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E42" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals +1.5</t>
+          <t>Under 10</t>
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.5866</v>
+        <v>0.6667000000000001</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-142</v>
+        <v>-200</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>102</v>
+        <v>-104</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -12409,7 +12475,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 58.7% (fair -142). Your call.</t>
+          <t>Model 66.7% (fair -200). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -12426,32 +12492,32 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Atlanta Braves -1.5</t>
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.5120943925233645</v>
+        <v>0.4134</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>-105</v>
+        <v>142</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>-114</v>
+        <v>133</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -12475,7 +12541,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 41.3% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -12492,32 +12558,32 @@
       </c>
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C44" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E44" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>St. Louis Cardinals +1.5</t>
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.487887323943662</v>
+        <v>0.5866</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>105</v>
+        <v>-142</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -12541,7 +12607,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -12568,22 +12634,22 @@
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Over 10.5</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.3925</v>
+        <v>0.5218909090909091</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>155</v>
+        <v>-109</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>108</v>
+        <v>-120</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -12607,7 +12673,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 39.2% (fair +155). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -12634,22 +12700,22 @@
       </c>
       <c r="D46" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E46" s="20" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.6074999999999999</v>
+        <v>0.4781447963800905</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-155</v>
+        <v>109</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -12673,7 +12739,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 60.7% (fair -155). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -12690,7 +12756,7 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
@@ -12700,22 +12766,22 @@
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Over 10.5</t>
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.3798062015503876</v>
+        <v>0.4482159624413146</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>163</v>
+        <v>123</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>158</v>
+        <v>113</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -12739,7 +12805,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 38.0% (fair +163). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -12756,7 +12822,7 @@
       </c>
       <c r="B48" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C48" s="20" t="inlineStr">
@@ -12766,22 +12832,22 @@
       </c>
       <c r="D48" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E48" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.6202057034220532</v>
+        <v>0.5517878048780488</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-163</v>
+        <v>-123</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>-163</v>
+        <v>-105</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -12805,7 +12871,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 62.0% (fair -163). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -12832,22 +12898,22 @@
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.4656</v>
+        <v>0.381015625</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>115</v>
+        <v>162</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>109</v>
+        <v>156</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -12871,7 +12937,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 38.1% (fair +162). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -12898,22 +12964,22 @@
       </c>
       <c r="D50" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E50" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.5344</v>
+        <v>0.6189661596958175</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-115</v>
+        <v>-162</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>113</v>
+        <v>-163</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -12937,7 +13003,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -115). Your call.</t>
+          <t>Model 61.9% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -12964,22 +13030,22 @@
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers -1.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.4955</v>
+        <v>0.4656</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -13003,7 +13069,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 49.5% (fair +102). Your call.</t>
+          <t>Model 46.6% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13030,22 +13096,22 @@
       </c>
       <c r="D52" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E52" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds +1.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.5344</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-102</v>
+        <v>-115</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -13069,7 +13135,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -102). Your call.</t>
+          <t>Model 53.4% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13086,32 +13152,32 @@
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Chicago Cubs</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Milwaukee Brewers -1.5</t>
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.4234873949579832</v>
+        <v>0.4612000000000001</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -13135,7 +13201,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 42.3% (fair +136). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -13152,32 +13218,32 @@
       </c>
       <c r="B54" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Chicago Cubs</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C54" s="20" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D54" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E54" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Cincinnati Reds +1.5</t>
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.5764689075630252</v>
+        <v>0.538826872246696</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-136</v>
+        <v>-117</v>
       </c>
       <c r="H54" s="15" t="n">
-        <v>-138</v>
+        <v>-127</v>
       </c>
       <c r="I54" s="13">
         <f>IF($H$54="","",IF($H$54&lt;0,-$H$54/(-$H$54+100),100/($H$54+100)))</f>
@@ -13201,7 +13267,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -13228,22 +13294,22 @@
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>Over 11.5</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.2296</v>
+        <v>0.4234873949579832</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>336</v>
+        <v>136</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -13267,7 +13333,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 23.0% (fair +336). Your call.</t>
+          <t>Model 42.3% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -13294,22 +13360,22 @@
       </c>
       <c r="D56" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E56" s="20" t="inlineStr">
         <is>
-          <t>Under 11.5</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.7704</v>
+        <v>0.5764689075630252</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>-336</v>
+        <v>-136</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>100</v>
+        <v>-138</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -13333,7 +13399,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 77.0% (fair -336). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -13360,22 +13426,22 @@
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs -1.5</t>
+          <t>Over 11.5</t>
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.4289270386266094</v>
+        <v>0.2296</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>133</v>
+        <v>336</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -13399,7 +13465,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 42.9% (fair +133). Your call.</t>
+          <t>Model 23.0% (fair +336). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -13426,22 +13492,22 @@
       </c>
       <c r="D58" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E58" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres +1.5</t>
+          <t>Under 11.5</t>
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.5710437768240343</v>
+        <v>0.7704</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-133</v>
+        <v>-336</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>-133</v>
+        <v>-101</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -13465,7 +13531,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 77.0% (fair -336). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -13482,31 +13548,33 @@
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Houston Astros</t>
+          <t>San Diego Padres @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Chicago Cubs -1.5</t>
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.6331</v>
+        <v>0.4289270386266094</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>-173</v>
-      </c>
-      <c r="H59" s="15" t="n"/>
+        <v>133</v>
+      </c>
+      <c r="H59" s="15" t="n">
+        <v>133</v>
+      </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
         <v/>
@@ -13529,7 +13597,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 63.3% (fair -173). Your call.</t>
+          <t>Model 42.9% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -13546,31 +13614,33 @@
       </c>
       <c r="B60" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Houston Astros</t>
+          <t>San Diego Padres @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C60" s="20" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D60" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E60" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>San Diego Padres +1.5</t>
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.3669</v>
+        <v>0.5710437768240343</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>173</v>
-      </c>
-      <c r="H60" s="15" t="n"/>
+        <v>-133</v>
+      </c>
+      <c r="H60" s="15" t="n">
+        <v>-133</v>
+      </c>
       <c r="I60" s="13">
         <f>IF($H$60="","",IF($H$60&lt;0,-$H$60/(-$H$60+100),100/($H$60+100)))</f>
         <v/>
@@ -13593,7 +13663,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 36.7% (fair +173). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -13610,12 +13680,12 @@
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Colorado Rockies</t>
+          <t>Minnesota Twins @ Houston Astros</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
@@ -13625,14 +13695,14 @@
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.4589</v>
+        <v>0.6331</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>118</v>
+        <v>-173</v>
       </c>
       <c r="H61" s="15" t="n"/>
       <c r="I61" s="13">
@@ -13657,7 +13727,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 63.3% (fair -173). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -13674,12 +13744,12 @@
       </c>
       <c r="B62" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Colorado Rockies</t>
+          <t>Minnesota Twins @ Houston Astros</t>
         </is>
       </c>
       <c r="C62" s="20" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D62" s="20" t="inlineStr">
@@ -13689,14 +13759,14 @@
       </c>
       <c r="E62" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.5411</v>
+        <v>0.3669</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>-118</v>
+        <v>173</v>
       </c>
       <c r="H62" s="15" t="n"/>
       <c r="I62" s="13">
@@ -13721,7 +13791,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 36.7% (fair +173). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -13738,12 +13808,12 @@
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers @ Athletics</t>
+          <t>Miami Marlins @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
@@ -13753,14 +13823,14 @@
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.6027</v>
+        <v>0.4589</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>-152</v>
+        <v>118</v>
       </c>
       <c r="H63" s="15" t="n"/>
       <c r="I63" s="13">
@@ -13785,7 +13855,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 60.3% (fair -152). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -13802,12 +13872,12 @@
       </c>
       <c r="B64" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers @ Athletics</t>
+          <t>Miami Marlins @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C64" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="D64" s="20" t="inlineStr">
@@ -13817,14 +13887,14 @@
       </c>
       <c r="E64" s="20" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.3973</v>
+        <v>0.5411</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>152</v>
+        <v>-118</v>
       </c>
       <c r="H64" s="15" t="n"/>
       <c r="I64" s="13">
@@ -13849,7 +13919,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 39.7% (fair +152). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -13866,7 +13936,7 @@
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Seattle Mariners</t>
+          <t>Los Angeles Dodgers @ Athletics</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
@@ -13881,14 +13951,14 @@
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.4286</v>
+        <v>0.6044</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>133</v>
+        <v>-153</v>
       </c>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="13">
@@ -13913,7 +13983,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 42.9% (fair +133). Your call.</t>
+          <t>Model 60.4% (fair -153). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -13930,7 +14000,7 @@
       </c>
       <c r="B66" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Seattle Mariners</t>
+          <t>Los Angeles Dodgers @ Athletics</t>
         </is>
       </c>
       <c r="C66" s="20" t="inlineStr">
@@ -13945,14 +14015,14 @@
       </c>
       <c r="E66" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5714</v>
+        <v>0.3956</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-133</v>
+        <v>153</v>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13">
@@ -13977,7 +14047,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 39.6% (fair +153). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -13994,7 +14064,7 @@
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Arizona Diamondbacks</t>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
@@ -14009,14 +14079,14 @@
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.5942</v>
+        <v>0.4286</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>-146</v>
+        <v>133</v>
       </c>
       <c r="H67" s="15" t="n"/>
       <c r="I67" s="13">
@@ -14041,7 +14111,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 59.4% (fair -146). Your call.</t>
+          <t>Model 42.9% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -14058,7 +14128,7 @@
       </c>
       <c r="B68" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Arizona Diamondbacks</t>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C68" s="20" t="inlineStr">
@@ -14073,14 +14143,14 @@
       </c>
       <c r="E68" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.4058</v>
+        <v>0.5714</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>146</v>
+        <v>-133</v>
       </c>
       <c r="H68" s="15" t="n"/>
       <c r="I68" s="13">
@@ -14105,7 +14175,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 40.6% (fair +146). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -14117,17 +14187,17 @@
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Baltimore Orioles</t>
+          <t>San Francisco Giants @ Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
@@ -14137,18 +14207,16 @@
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.4761290322580645</v>
+        <v>0.5926</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>110</v>
-      </c>
-      <c r="H69" s="15" t="n">
-        <v>117</v>
-      </c>
+        <v>-145</v>
+      </c>
+      <c r="H69" s="15" t="n"/>
       <c r="I69" s="13">
         <f>IF($H$69="","",IF($H$69&lt;0,-$H$69/(-$H$69+100),100/($H$69+100)))</f>
         <v/>
@@ -14171,7 +14239,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 59.3% (fair -145). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -14183,17 +14251,17 @@
     <row r="70">
       <c r="A70" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B70" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Baltimore Orioles</t>
+          <t>San Francisco Giants @ Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="C70" s="20" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D70" s="20" t="inlineStr">
@@ -14203,18 +14271,16 @@
       </c>
       <c r="E70" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.5238855855855856</v>
+        <v>0.4074</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>-110</v>
-      </c>
-      <c r="H70" s="15" t="n">
-        <v>-122</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="H70" s="15" t="n"/>
       <c r="I70" s="13">
         <f>IF($H$70="","",IF($H$70&lt;0,-$H$70/(-$H$70+100),100/($H$70+100)))</f>
         <v/>
@@ -14237,7 +14303,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 40.7% (fair +145). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -14254,12 +14320,12 @@
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>Chicago White Sox @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
@@ -14269,17 +14335,17 @@
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.4987980769230769</v>
+        <v>0.4761290322580645</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H71" s="15" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="I71" s="13">
         <f>IF($H$71="","",IF($H$71&lt;0,-$H$71/(-$H$71+100),100/($H$71+100)))</f>
@@ -14303,7 +14369,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +100). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -14320,12 +14386,12 @@
       </c>
       <c r="B72" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>Chicago White Sox @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C72" s="20" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="D72" s="20" t="inlineStr">
@@ -14335,17 +14401,17 @@
       </c>
       <c r="E72" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.5012134615384616</v>
+        <v>0.5238855855855856</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>-100</v>
+        <v>-110</v>
       </c>
       <c r="H72" s="15" t="n">
-        <v>-108</v>
+        <v>-122</v>
       </c>
       <c r="I72" s="13">
         <f>IF($H$72="","",IF($H$72&lt;0,-$H$72/(-$H$72+100),100/($H$72+100)))</f>
@@ -14369,7 +14435,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -100). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -14386,12 +14452,12 @@
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Boston Red Sox</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
@@ -14401,17 +14467,17 @@
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.4783</v>
+        <v>0.4987980769230769</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="I73" s="13">
         <f>IF($H$73="","",IF($H$73&lt;0,-$H$73/(-$H$73+100),100/($H$73+100)))</f>
@@ -14435,7 +14501,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 49.9% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -14452,12 +14518,12 @@
       </c>
       <c r="B74" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Boston Red Sox</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C74" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="D74" s="20" t="inlineStr">
@@ -14467,17 +14533,17 @@
       </c>
       <c r="E74" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.5217000000000001</v>
+        <v>0.5012134615384616</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>-109</v>
+        <v>-100</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>117</v>
+        <v>-108</v>
       </c>
       <c r="I74" s="13">
         <f>IF($H$74="","",IF($H$74&lt;0,-$H$74/(-$H$74+100),100/($H$74+100)))</f>
@@ -14501,7 +14567,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
+          <t>Model 50.1% (fair -100). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -14518,7 +14584,7 @@
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>Washington Nationals @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
@@ -14533,17 +14599,17 @@
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.4195081967213115</v>
+        <v>0.4783</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>138</v>
+        <v>109</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -14567,7 +14633,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 42.0% (fair +138). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -14584,7 +14650,7 @@
       </c>
       <c r="B76" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>Washington Nationals @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C76" s="20" t="inlineStr">
@@ -14599,17 +14665,17 @@
       </c>
       <c r="E76" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.5805277310924369</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-138</v>
+        <v>-109</v>
       </c>
       <c r="H76" s="15" t="n">
-        <v>-138</v>
+        <v>117</v>
       </c>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
@@ -14633,7 +14699,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 58.1% (fair -138). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -14650,12 +14716,12 @@
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Chicago Cubs</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
@@ -14665,17 +14731,17 @@
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.4883173076923077</v>
+        <v>0.4195081967213115</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>105</v>
+        <v>138</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="I77" s="13">
         <f>IF($H$77="","",IF($H$77&lt;0,-$H$77/(-$H$77+100),100/($H$77+100)))</f>
@@ -14699,7 +14765,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 42.0% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -14716,12 +14782,12 @@
       </c>
       <c r="B78" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Chicago Cubs</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C78" s="20" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
@@ -14731,17 +14797,17 @@
       </c>
       <c r="E78" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.51165</v>
+        <v>0.5805277310924369</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-105</v>
+        <v>-138</v>
       </c>
       <c r="H78" s="15" t="n">
-        <v>-108</v>
+        <v>-138</v>
       </c>
       <c r="I78" s="13">
         <f>IF($H$78="","",IF($H$78&lt;0,-$H$78/(-$H$78+100),100/($H$78+100)))</f>
@@ -14765,7 +14831,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 58.1% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -14782,12 +14848,12 @@
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Toronto Blue Jays</t>
+          <t>San Diego Padres @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
@@ -14797,17 +14863,17 @@
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.5072549019607843</v>
+        <v>0.4883173076923077</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>-103</v>
+        <v>105</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -14831,7 +14897,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 50.7% (fair -103). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -14848,12 +14914,12 @@
       </c>
       <c r="B80" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Toronto Blue Jays</t>
+          <t>San Diego Padres @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C80" s="20" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
@@ -14863,17 +14929,17 @@
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.4927450980392157</v>
+        <v>0.51165</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>103</v>
+        <v>-105</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>104</v>
+        <v>-108</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -14897,7 +14963,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 49.3% (fair +103). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -14914,12 +14980,12 @@
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>New York Mets @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
@@ -14929,17 +14995,17 @@
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.465726872246696</v>
+        <v>0.5208</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>115</v>
+        <v>-109</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -14963,7 +15029,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -14980,12 +15046,12 @@
       </c>
       <c r="B82" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>New York Mets @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C82" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
@@ -14995,17 +15061,17 @@
       </c>
       <c r="E82" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.534295154185022</v>
+        <v>0.4793</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>-115</v>
+        <v>109</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>-127</v>
+        <v>108</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -15029,7 +15095,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -115). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -15046,12 +15112,12 @@
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Atlanta Braves</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
@@ -15061,17 +15127,17 @@
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.4461764705882353</v>
+        <v>0.465726872246696</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -15095,7 +15161,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 44.6% (fair +124). Your call.</t>
+          <t>Model 46.6% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -15112,12 +15178,12 @@
       </c>
       <c r="B84" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Atlanta Braves</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C84" s="20" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
@@ -15127,17 +15193,17 @@
       </c>
       <c r="E84" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.5538688524590164</v>
+        <v>0.534295154185022</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>-124</v>
+        <v>-115</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>-144</v>
+        <v>-127</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -15161,7 +15227,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 55.4% (fair -124). Your call.</t>
+          <t>Model 53.4% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -15178,12 +15244,12 @@
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
@@ -15193,17 +15259,17 @@
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.5363603603603604</v>
+        <v>0.4422131147540984</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>-116</v>
+        <v>126</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>-122</v>
+        <v>144</v>
       </c>
       <c r="I85" s="13">
         <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
@@ -15227,7 +15293,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 53.6% (fair -116). Your call.</t>
+          <t>Model 44.2% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -15244,12 +15310,12 @@
       </c>
       <c r="B86" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C86" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D86" s="20" t="inlineStr">
@@ -15259,17 +15325,17 @@
       </c>
       <c r="E86" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.4636563876651982</v>
+        <v>0.5577639344262295</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>116</v>
+        <v>-126</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>127</v>
+        <v>-144</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -15293,7 +15359,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 46.4% (fair +116). Your call.</t>
+          <t>Model 55.8% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -15310,12 +15376,12 @@
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Houston Astros</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
@@ -15325,17 +15391,17 @@
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.4990610328638498</v>
+        <v>0.5016</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>100</v>
+        <v>-101</v>
       </c>
       <c r="H87" s="15" t="n">
-        <v>113</v>
+        <v>-122</v>
       </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
@@ -15359,7 +15425,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +100). Your call.</t>
+          <t>Model 50.2% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -15376,12 +15442,12 @@
       </c>
       <c r="B88" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Houston Astros</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C88" s="20" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D88" s="20" t="inlineStr">
@@ -15391,17 +15457,17 @@
       </c>
       <c r="E88" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.5009136150234742</v>
+        <v>0.4984</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>-100</v>
+        <v>101</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>-113</v>
+        <v>133</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -15425,7 +15491,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -100). Your call.</t>
+          <t>Model 49.8% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -15442,7 +15508,7 @@
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Minnesota Twins @ Houston Astros</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
@@ -15457,16 +15523,18 @@
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.3364</v>
+        <v>0.4990610328638498</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>197</v>
-      </c>
-      <c r="H89" s="15" t="n"/>
+        <v>100</v>
+      </c>
+      <c r="H89" s="15" t="n">
+        <v>113</v>
+      </c>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
         <v/>
@@ -15489,7 +15557,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 33.6% (fair +197). Your call.</t>
+          <t>Model 49.9% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -15506,7 +15574,7 @@
       </c>
       <c r="B90" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Minnesota Twins @ Houston Astros</t>
         </is>
       </c>
       <c r="C90" s="20" t="inlineStr">
@@ -15521,16 +15589,18 @@
       </c>
       <c r="E90" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.6636</v>
+        <v>0.5009136150234742</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>-197</v>
-      </c>
-      <c r="H90" s="15" t="n"/>
+        <v>-100</v>
+      </c>
+      <c r="H90" s="15" t="n">
+        <v>-113</v>
+      </c>
       <c r="I90" s="13">
         <f>IF($H$90="","",IF($H$90&lt;0,-$H$90/(-$H$90+100),100/($H$90+100)))</f>
         <v/>
@@ -15553,7 +15623,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 66.4% (fair -197). Your call.</t>
+          <t>Model 50.1% (fair -100). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -15570,12 +15640,12 @@
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Colorado Rockies</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
@@ -15585,14 +15655,14 @@
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.5847</v>
+        <v>0.3364</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>-141</v>
+        <v>197</v>
       </c>
       <c r="H91" s="15" t="n"/>
       <c r="I91" s="13">
@@ -15617,7 +15687,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 58.5% (fair -141). Your call.</t>
+          <t>Model 33.6% (fair +197). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -15634,12 +15704,12 @@
       </c>
       <c r="B92" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Colorado Rockies</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C92" s="20" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D92" s="20" t="inlineStr">
@@ -15649,14 +15719,14 @@
       </c>
       <c r="E92" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.4153</v>
+        <v>0.6636</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>141</v>
+        <v>-197</v>
       </c>
       <c r="H92" s="15" t="n"/>
       <c r="I92" s="13">
@@ -15681,7 +15751,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 41.5% (fair +141). Your call.</t>
+          <t>Model 66.4% (fair -197). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -15698,12 +15768,12 @@
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers @ Athletics</t>
+          <t>Miami Marlins @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
@@ -15713,14 +15783,14 @@
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.5725</v>
+        <v>0.5847</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>-134</v>
+        <v>-141</v>
       </c>
       <c r="H93" s="15" t="n"/>
       <c r="I93" s="13">
@@ -15745,7 +15815,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
+          <t>Model 58.5% (fair -141). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -15762,12 +15832,12 @@
       </c>
       <c r="B94" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers @ Athletics</t>
+          <t>Miami Marlins @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C94" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="D94" s="20" t="inlineStr">
@@ -15777,14 +15847,14 @@
       </c>
       <c r="E94" s="20" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.4275</v>
+        <v>0.4153</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="H94" s="15" t="n"/>
       <c r="I94" s="13">
@@ -15809,7 +15879,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 42.8% (fair +134). Your call.</t>
+          <t>Model 41.5% (fair +141). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -15826,7 +15896,7 @@
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Arizona Diamondbacks</t>
+          <t>Los Angeles Dodgers @ Athletics</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
@@ -15841,14 +15911,14 @@
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.5942</v>
+        <v>0.5732</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>-146</v>
+        <v>-134</v>
       </c>
       <c r="H95" s="15" t="n"/>
       <c r="I95" s="13">
@@ -15873,7 +15943,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 59.4% (fair -146). Your call.</t>
+          <t>Model 57.3% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -15890,7 +15960,7 @@
       </c>
       <c r="B96" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Arizona Diamondbacks</t>
+          <t>Los Angeles Dodgers @ Athletics</t>
         </is>
       </c>
       <c r="C96" s="20" t="inlineStr">
@@ -15905,14 +15975,14 @@
       </c>
       <c r="E96" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.4058</v>
+        <v>0.4268</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="H96" s="15" t="n"/>
       <c r="I96" s="13">
@@ -15937,7 +16007,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 40.6% (fair +146). Your call.</t>
+          <t>Model 42.7% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -15946,9 +16016,137 @@
         <v/>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B97" s="12" t="inlineStr">
+        <is>
+          <t>San Francisco Giants @ Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="C97" s="12" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="D97" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E97" s="12" t="inlineStr">
+        <is>
+          <t>San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="F97" s="13" t="n">
+        <v>0.5901999999999999</v>
+      </c>
+      <c r="G97" s="14" t="n">
+        <v>-144</v>
+      </c>
+      <c r="H97" s="15" t="n"/>
+      <c r="I97" s="13">
+        <f>IF($H$97="","",IF($H$97&lt;0,-$H$97/(-$H$97+100),100/($H$97+100)))</f>
+        <v/>
+      </c>
+      <c r="J97" s="16">
+        <f>IF($H$97="","",$F$97*IF($H$97&lt;0,-100/$H$97,$H$97/100)-(1-$F$97))</f>
+        <v/>
+      </c>
+      <c r="K97" s="17">
+        <f>IF($H$97="","",MAX(0,($F$97*IF($H$97&lt;0,-100/$H$97,$H$97/100)-(1-$F$97))/IF($H$97&lt;0,-100/$H$97,$H$97/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L97" s="18">
+        <f>IF($H$97="","",ROUND(MIN($K$97,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M97" s="12">
+        <f>IF($J$97="","",IF($J$97&lt;0,"Pass",IF($J$97&lt;'Settings'!$B$4,"Thin",IF($J$97&lt;0.06,"✅ Sharp band",IF($J$97&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N97" s="19" t="inlineStr">
+        <is>
+          <t>Model 59.0% (fair -144). Your call.</t>
+        </is>
+      </c>
+      <c r="O97" s="15" t="n"/>
+      <c r="P97" s="16">
+        <f>IF(OR($H$97="",$O$97=""),"",(1+IF($H$97&lt;0,-100/$H$97,$H$97/100))/(1+IF($O$97&lt;0,-100/$O$97,$O$97/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B98" s="20" t="inlineStr">
+        <is>
+          <t>San Francisco Giants @ Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="C98" s="20" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="D98" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E98" s="20" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="F98" s="13" t="n">
+        <v>0.4098</v>
+      </c>
+      <c r="G98" s="14" t="n">
+        <v>144</v>
+      </c>
+      <c r="H98" s="15" t="n"/>
+      <c r="I98" s="13">
+        <f>IF($H$98="","",IF($H$98&lt;0,-$H$98/(-$H$98+100),100/($H$98+100)))</f>
+        <v/>
+      </c>
+      <c r="J98" s="16">
+        <f>IF($H$98="","",$F$98*IF($H$98&lt;0,-100/$H$98,$H$98/100)-(1-$F$98))</f>
+        <v/>
+      </c>
+      <c r="K98" s="17">
+        <f>IF($H$98="","",MAX(0,($F$98*IF($H$98&lt;0,-100/$H$98,$H$98/100)-(1-$F$98))/IF($H$98&lt;0,-100/$H$98,$H$98/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L98" s="18">
+        <f>IF($H$98="","",ROUND(MIN($K$98,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M98" s="12">
+        <f>IF($J$98="","",IF($J$98&lt;0,"Pass",IF($J$98&lt;'Settings'!$B$4,"Thin",IF($J$98&lt;0.06,"✅ Sharp band",IF($J$98&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N98" s="19" t="inlineStr">
+        <is>
+          <t>Model 41.0% (fair +144). Your call.</t>
+        </is>
+      </c>
+      <c r="O98" s="15" t="n"/>
+      <c r="P98" s="16">
+        <f>IF(OR($H$98="",$O$98=""),"",(1+IF($H$98&lt;0,-100/$H$98,$H$98/100))/(1+IF($O$98&lt;0,-100/$O$98,$O$98/100))-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J96">
+  <conditionalFormatting sqref="J5:J98">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -17699,7 +17897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:Q73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17716,174 +17914,328 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="29" t="inlineStr">
+        <is>
+          <t>Texas Rangers offense vs Cleveland Guardians defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B60" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C60" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D60" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E60" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F60" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G60" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H60" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I60" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J60" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K60" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L60" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M60" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N60" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O60" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P60" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q60" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="61">
-      <c r="A61" s="29" t="inlineStr">
-        <is>
-          <t>Texas Rangers offense vs Cleveland Guardians defense</t>
+      <c r="A61" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B61" s="32" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="C61" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D61" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E61" s="32" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="F61" s="32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G61" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H61" s="33" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="I61" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J61" s="36" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="K61" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="L61" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="M61" s="32" t="n">
+        <v>3.733</v>
+      </c>
+      <c r="N61" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O61" s="32" t="n">
+        <v>4.533</v>
+      </c>
+      <c r="P61" s="32" t="n">
+        <v>4.133</v>
+      </c>
+      <c r="Q61" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B62" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C62" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D62" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E62" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F62" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G62" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H62" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I62" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J62" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K62" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L62" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M62" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N62" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O62" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P62" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q62" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A62" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B62" s="32" t="n">
+        <v>7.816</v>
+      </c>
+      <c r="C62" s="32" t="n">
+        <v>9.167</v>
+      </c>
+      <c r="D62" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E62" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F62" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G62" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H62" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I62" s="32" t="inlineStr"/>
+      <c r="J62" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K62" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L62" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M62" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N62" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O62" s="32" t="n">
+        <v>10.429</v>
+      </c>
+      <c r="P62" s="32" t="n">
+        <v>7.939</v>
+      </c>
+      <c r="Q62" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B63" s="32" t="n">
-        <v>4.15</v>
+        <v>1.041</v>
       </c>
       <c r="C63" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="D63" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E63" s="32" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="F63" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G63" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H63" s="33" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I63" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J63" s="36" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="K63" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="L63" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="M63" s="32" t="n">
-        <v>3.733</v>
-      </c>
-      <c r="N63" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O63" s="32" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="P63" s="32" t="n">
-        <v>4.133</v>
+        <v>1</v>
+      </c>
+      <c r="D63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H63" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I63" s="32" t="inlineStr"/>
+      <c r="J63" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q63" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B64" s="32" t="n">
-        <v>7.816</v>
+        <v>8.592000000000001</v>
       </c>
       <c r="C64" s="32" t="n">
-        <v>9.167</v>
+        <v>8.833</v>
       </c>
       <c r="D64" s="32" t="inlineStr">
         <is>
@@ -17937,398 +18289,398 @@
         </is>
       </c>
       <c r="O64" s="32" t="n">
-        <v>10.429</v>
+        <v>9</v>
       </c>
       <c r="P64" s="32" t="n">
-        <v>7.939</v>
+        <v>9.388</v>
       </c>
       <c r="Q64" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B65" s="32" t="n">
-        <v>1.041</v>
+        <v>0.63</v>
       </c>
       <c r="C65" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H65" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I65" s="32" t="inlineStr"/>
-      <c r="J65" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.867</v>
+      </c>
+      <c r="D65" s="32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E65" s="32" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="F65" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G65" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H65" s="33" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="I65" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J65" s="33" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="K65" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M65" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N65" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O65" s="32" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="P65" s="32" t="n">
+        <v>0.375</v>
       </c>
       <c r="Q65" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B66" s="32" t="n">
-        <v>8.592000000000001</v>
-      </c>
-      <c r="C66" s="32" t="n">
-        <v>8.833</v>
-      </c>
-      <c r="D66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H66" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I66" s="32" t="inlineStr"/>
-      <c r="J66" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O66" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="P66" s="32" t="n">
-        <v>9.388</v>
-      </c>
-      <c r="Q66" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B67" s="32" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="C67" s="32" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="D67" s="32" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E67" s="32" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="F67" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G67" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H67" s="33" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="I67" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J67" s="33" t="inlineStr">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians offense vs Texas Rangers defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H69" s="34" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr"/>
+      <c r="J69" s="33" t="inlineStr">
         <is>
           <t>8th</t>
         </is>
       </c>
-      <c r="K67" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M67" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N67" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O67" s="32" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="P67" s="32" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="Q67" s="35" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians offense vs Texas Rangers defense</t>
+      <c r="K69" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>4.533</v>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>4.138</v>
+      </c>
+      <c r="Q69" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>7.735</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>9.143000000000001</v>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>8.167</v>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>7.673</v>
+      </c>
+      <c r="Q70" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>3.88</v>
+        <v>0.959</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D71" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E71" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="F71" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G71" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>22nd</t>
+        <v>0.286</v>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="33" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L71" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="M71" s="32" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="N71" s="32" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="O71" s="32" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="P71" s="32" t="n">
-        <v>4.138</v>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>7.735</v>
+        <v>8</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>9.143000000000001</v>
+        <v>9.429</v>
       </c>
       <c r="D72" s="32" t="inlineStr">
         <is>
@@ -18382,225 +18734,71 @@
         </is>
       </c>
       <c r="O72" s="32" t="n">
-        <v>8.167</v>
+        <v>9.167</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>7.673</v>
+        <v>8.571</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>0.959</v>
+        <v>0.5</v>
       </c>
       <c r="C73" s="32" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="D73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.3</v>
+      </c>
+      <c r="D73" s="32" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E73" s="32" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="F73" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G73" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H73" s="36" t="inlineStr">
+        <is>
+          <t>19th</t>
         </is>
       </c>
       <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J73" s="33" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>0.781</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="C74" s="32" t="n">
-        <v>9.429</v>
-      </c>
-      <c r="D74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="32" t="n">
-        <v>9.167</v>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>8.571</v>
-      </c>
-      <c r="Q74" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D75" s="32" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E75" s="32" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="F75" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H75" s="36" t="inlineStr">
-        <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="33" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" s="32" t="n">
-        <v>0.9330000000000001</v>
-      </c>
-      <c r="N75" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>0.781</v>
-      </c>
-      <c r="Q75" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>

--- a/data/output/workbook/2026-06-30.xlsx
+++ b/data/output/workbook/2026-06-30.xlsx
@@ -371,7 +371,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="9229725"/>
+    <ext cx="10125075" cy="9429750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -401,7 +401,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="9086850"/>
+    <ext cx="10125075" cy="9467850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30 07:45</t>
+          <t>2026-06-30 10:15</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:Q75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7619,324 +7619,170 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="29" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="29" t="inlineStr">
         <is>
           <t>San Diego Padres offense vs Chicago Cubs defense</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="30" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B60" s="30" t="inlineStr">
+      <c r="B62" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C60" s="30" t="inlineStr">
+      <c r="C62" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D60" s="30" t="inlineStr">
+      <c r="D62" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E60" s="30" t="inlineStr">
+      <c r="E62" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F60" s="30" t="inlineStr">
+      <c r="F62" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G60" s="30" t="inlineStr">
+      <c r="G62" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H60" s="30" t="inlineStr">
+      <c r="H62" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I60" s="30" t="inlineStr">
+      <c r="I62" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J60" s="30" t="inlineStr">
+      <c r="J62" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K60" s="30" t="inlineStr">
+      <c r="K62" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L60" s="30" t="inlineStr">
+      <c r="L62" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M60" s="30" t="inlineStr">
+      <c r="M62" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N60" s="30" t="inlineStr">
+      <c r="N62" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O60" s="30" t="inlineStr">
+      <c r="O62" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P60" s="30" t="inlineStr">
+      <c r="P62" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q60" s="30" t="inlineStr">
+      <c r="Q62" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B61" s="32" t="n">
-        <v>3.987</v>
-      </c>
-      <c r="C61" s="32" t="n">
-        <v>3.733</v>
-      </c>
-      <c r="D61" s="32" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="E61" s="32" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="F61" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G61" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H61" s="36" t="inlineStr">
-        <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="I61" s="32" t="inlineStr"/>
-      <c r="J61" s="33" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-      <c r="K61" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L61" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="M61" s="32" t="n">
-        <v>4.067</v>
-      </c>
-      <c r="N61" s="32" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O61" s="32" t="n">
-        <v>4.267</v>
-      </c>
-      <c r="P61" s="32" t="n">
-        <v>4.644</v>
-      </c>
-      <c r="Q61" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B62" s="32" t="n">
-        <v>7.087</v>
-      </c>
-      <c r="C62" s="32" t="n">
-        <v>6.833</v>
-      </c>
-      <c r="D62" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E62" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F62" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G62" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H62" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I62" s="32" t="inlineStr"/>
-      <c r="J62" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K62" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L62" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M62" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N62" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O62" s="32" t="n">
-        <v>6.833</v>
-      </c>
-      <c r="P62" s="32" t="n">
-        <v>7.896</v>
-      </c>
-      <c r="Q62" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B63" s="32" t="n">
-        <v>1.022</v>
+        <v>3.987</v>
       </c>
       <c r="C63" s="32" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="D63" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E63" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F63" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G63" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H63" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>3.733</v>
+      </c>
+      <c r="D63" s="32" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E63" s="32" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="F63" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G63" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H63" s="36" t="inlineStr">
+        <is>
+          <t>19th</t>
         </is>
       </c>
       <c r="I63" s="32" t="inlineStr"/>
-      <c r="J63" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K63" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L63" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M63" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N63" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O63" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P63" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J63" s="33" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="K63" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L63" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="M63" s="32" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="N63" s="32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O63" s="32" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="P63" s="32" t="n">
+        <v>4.644</v>
       </c>
       <c r="Q63" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B64" s="32" t="n">
-        <v>8.348000000000001</v>
+        <v>7.087</v>
       </c>
       <c r="C64" s="32" t="n">
-        <v>9.333</v>
+        <v>6.833</v>
       </c>
       <c r="D64" s="32" t="inlineStr">
         <is>
@@ -7990,398 +7836,398 @@
         </is>
       </c>
       <c r="O64" s="32" t="n">
-        <v>7</v>
+        <v>6.833</v>
       </c>
       <c r="P64" s="32" t="n">
-        <v>7.708</v>
+        <v>7.896</v>
       </c>
       <c r="Q64" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B65" s="32" t="n">
+        <v>1.022</v>
+      </c>
+      <c r="C65" s="32" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="D65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H65" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I65" s="32" t="inlineStr"/>
+      <c r="J65" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q65" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B66" s="32" t="n">
+        <v>8.348000000000001</v>
+      </c>
+      <c r="C66" s="32" t="n">
+        <v>9.333</v>
+      </c>
+      <c r="D66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H66" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I66" s="32" t="inlineStr"/>
+      <c r="J66" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O66" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="P66" s="32" t="n">
+        <v>7.708</v>
+      </c>
+      <c r="Q66" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B65" s="32" t="n">
+      <c r="B67" s="32" t="n">
         <v>0.329</v>
       </c>
-      <c r="C65" s="32" t="n">
+      <c r="C67" s="32" t="n">
         <v>0.433</v>
       </c>
-      <c r="D65" s="32" t="n">
+      <c r="D67" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="E65" s="32" t="n">
+      <c r="E67" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="F65" s="32" t="n">
+      <c r="F67" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="G65" s="32" t="n">
+      <c r="G67" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H65" s="34" t="inlineStr">
+      <c r="H67" s="34" t="inlineStr">
         <is>
           <t>27th</t>
         </is>
       </c>
-      <c r="I65" s="32" t="inlineStr"/>
-      <c r="J65" s="36" t="inlineStr">
+      <c r="I67" s="32" t="inlineStr"/>
+      <c r="J67" s="36" t="inlineStr">
         <is>
           <t>14th</t>
         </is>
       </c>
-      <c r="K65" s="32" t="n">
+      <c r="K67" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="L65" s="32" t="n">
+      <c r="L67" s="32" t="n">
         <v>0.1</v>
       </c>
-      <c r="M65" s="32" t="n">
+      <c r="M67" s="32" t="n">
         <v>0.067</v>
       </c>
-      <c r="N65" s="32" t="n">
+      <c r="N67" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="O65" s="32" t="n">
+      <c r="O67" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="P65" s="32" t="n">
+      <c r="P67" s="32" t="n">
         <v>0.444</v>
       </c>
-      <c r="Q65" s="35" t="inlineStr">
+      <c r="Q67" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="29" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>Chicago Cubs offense vs San Diego Padres defense</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="30" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B68" s="30" t="inlineStr">
+      <c r="B70" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C68" s="30" t="inlineStr">
+      <c r="C70" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D68" s="30" t="inlineStr">
+      <c r="D70" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E68" s="30" t="inlineStr">
+      <c r="E70" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F68" s="30" t="inlineStr">
+      <c r="F70" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G68" s="30" t="inlineStr">
+      <c r="G70" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H68" s="30" t="inlineStr">
+      <c r="H70" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I68" s="30" t="inlineStr">
+      <c r="I70" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J68" s="30" t="inlineStr">
+      <c r="J70" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K68" s="30" t="inlineStr">
+      <c r="K70" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L68" s="30" t="inlineStr">
+      <c r="L70" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M68" s="30" t="inlineStr">
+      <c r="M70" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N68" s="30" t="inlineStr">
+      <c r="N70" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O68" s="30" t="inlineStr">
+      <c r="O70" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P68" s="30" t="inlineStr">
+      <c r="P70" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q68" s="30" t="inlineStr">
+      <c r="Q70" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="n">
-        <v>5.027</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>5.367</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="E69" s="32" t="n">
-        <v>6.267</v>
-      </c>
-      <c r="F69" s="32" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="G69" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H69" s="36" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J69" s="34" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="L69" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="M69" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="N69" s="32" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="P69" s="32" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="Q69" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B70" s="32" t="n">
-        <v>8.438000000000001</v>
-      </c>
-      <c r="C70" s="32" t="n">
-        <v>9.333</v>
-      </c>
-      <c r="D70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O70" s="32" t="n">
-        <v>8.333</v>
-      </c>
-      <c r="P70" s="32" t="n">
-        <v>7.848</v>
-      </c>
-      <c r="Q70" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>1.104</v>
+        <v>5.027</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5.367</v>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>6.267</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H71" s="36" t="inlineStr">
+        <is>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J71" s="34" t="inlineStr">
+        <is>
+          <t>21st</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="L71" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M71" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="N71" s="32" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P71" s="32" t="n">
+        <v>3.87</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>8.458</v>
+        <v>8.438000000000001</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>8.833</v>
+        <v>9.333</v>
       </c>
       <c r="D72" s="32" t="inlineStr">
         <is>
@@ -8435,71 +8281,225 @@
         </is>
       </c>
       <c r="O72" s="32" t="n">
-        <v>4.833</v>
+        <v>8.333</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>8.304</v>
+        <v>7.848</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="n">
+        <v>1.104</v>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q73" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B74" s="32" t="n">
+        <v>8.458</v>
+      </c>
+      <c r="C74" s="32" t="n">
+        <v>8.833</v>
+      </c>
+      <c r="D74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="32" t="n">
+        <v>4.833</v>
+      </c>
+      <c r="P74" s="32" t="n">
+        <v>8.304</v>
+      </c>
+      <c r="Q74" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B73" s="32" t="n">
+      <c r="B75" s="32" t="n">
         <v>0.417</v>
       </c>
-      <c r="C73" s="32" t="n">
+      <c r="C75" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="D73" s="32" t="n">
+      <c r="D75" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="E73" s="32" t="n">
+      <c r="E75" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="F73" s="32" t="n">
+      <c r="F75" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="G73" s="32" t="n">
+      <c r="G75" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H73" s="34" t="inlineStr">
+      <c r="H75" s="34" t="inlineStr">
         <is>
           <t>29th</t>
         </is>
       </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="33" t="inlineStr">
+      <c r="I75" s="32" t="inlineStr"/>
+      <c r="J75" s="33" t="inlineStr">
         <is>
           <t>6th</t>
         </is>
       </c>
-      <c r="K73" s="32" t="n">
+      <c r="K75" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L73" s="32" t="n">
+      <c r="L75" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="M73" s="32" t="n">
+      <c r="M75" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="N73" s="32" t="n">
+      <c r="N75" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="O73" s="32" t="n">
+      <c r="O75" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="P73" s="32" t="n">
+      <c r="P75" s="32" t="n">
         <v>0.457</v>
       </c>
-      <c r="Q73" s="35" t="inlineStr">
+      <c r="Q75" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8848,37 +8848,37 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5517878048780488</v>
+        <v>0.4685903083700441</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-123</v>
+        <v>113</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-105</v>
+        <v>127</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 46.9% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -8980,17 +8980,17 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -9000,17 +9000,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.465726872246696</v>
+        <v>0.5569464454976303</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>115</v>
+        <v>-126</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>127</v>
+        <v>-111</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 55.7% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9046,7 +9046,7 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
@@ -9070,13 +9070,13 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.4781447963800905</v>
+        <v>0.4636563876651982</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -9100,7 +9100,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 46.4% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9117,32 +9117,32 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5112745098039215</v>
+        <v>0.4842396313364055</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-105</v>
+        <v>107</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9166,7 +9166,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -105). Your call.</t>
+          <t>Model 48.4% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9178,17 +9178,17 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -9198,17 +9198,17 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5728504504504505</v>
+        <v>0.4987980769230769</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-134</v>
+        <v>100</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-122</v>
+        <v>108</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 57.3% (fair -134). Your call.</t>
+          <t>Model 49.9% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9244,37 +9244,37 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>New York Mets @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5245930693069306</v>
+        <v>0.5072549019607843</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-110</v>
+        <v>-103</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>-102</v>
+        <v>104</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9298,7 +9298,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 52.5% (fair -110). Your call.</t>
+          <t>Model 50.7% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9310,37 +9310,37 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>San Diego Padres @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers -1.5</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4612000000000001</v>
+        <v>0.4845070422535211</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9364,7 +9364,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9376,17 +9376,17 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -9396,17 +9396,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4987980769230769</v>
+        <v>0.4318067226890757</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9430,7 +9430,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +100). Your call.</t>
+          <t>Model 43.2% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9447,12 +9447,12 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Atlanta Braves</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -9462,17 +9462,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4249590163934426</v>
+        <v>0.5335096153846154</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>135</v>
+        <v>-114</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>144</v>
+        <v>-108</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9496,7 +9496,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 42.5% (fair +135). Your call.</t>
+          <t>Model 53.4% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9508,7 +9508,7 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -9532,13 +9532,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4559911894273127</v>
+        <v>0.4732258064516129</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -9562,7 +9562,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 45.6% (fair +119). Your call.</t>
+          <t>Model 47.3% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9574,17 +9574,17 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Baltimore Orioles</t>
+          <t>New York Mets @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -9594,17 +9594,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4761290322580645</v>
+        <v>0.4935096153846154</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9628,7 +9628,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 49.4% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9640,17 +9640,17 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -9660,17 +9660,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5327307692307692</v>
+        <v>0.4195081967213115</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-114</v>
+        <v>138</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-108</v>
+        <v>144</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 53.3% (fair -114). Your call.</t>
+          <t>Model 42.0% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9706,37 +9706,37 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Pittsburgh Pirates +1.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4195081967213115</v>
+        <v>0.5017156862745098</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>138</v>
+        <v>-101</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 42.0% (fair +138). Your call.</t>
+          <t>Model 50.2% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9777,12 +9777,12 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Toronto Blue Jays</t>
+          <t>Chicago White Sox @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -9792,17 +9792,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4920192307692308</v>
+        <v>0.4606756756756757</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9826,7 +9826,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -10003,13 +10003,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.4559911894273127</v>
+        <v>0.4606756756756757</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -10033,7 +10033,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 45.6% (fair +119). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -10069,13 +10069,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5440299559471367</v>
+        <v>0.5393333333333333</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-119</v>
+        <v>-117</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-127</v>
+        <v>-125</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -10099,7 +10099,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 54.4% (fair -119). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -10141,7 +10141,7 @@
         <v>-124</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -10207,7 +10207,7 @@
         <v>124</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -10273,7 +10273,7 @@
         <v>155</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -10339,7 +10339,7 @@
         <v>-155</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -10399,7 +10399,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5327307692307692</v>
+        <v>0.5335096153846154</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>-114</v>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 53.3% (fair -114). Your call.</t>
+          <t>Model 53.4% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -10465,13 +10465,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4672946859903381</v>
+        <v>0.4664903846153846</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>114</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -10495,7 +10495,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 46.7% (fair +114). Your call.</t>
+          <t>Model 46.6% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -10527,17 +10527,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5245930693069306</v>
+        <v>0.4777</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-110</v>
+        <v>109</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>-102</v>
+        <v>110</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -10561,7 +10561,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 52.5% (fair -110). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -10593,17 +10593,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>Under 8</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4754411764705882</v>
+        <v>0.5223</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>110</v>
+        <v>-109</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -10627,7 +10627,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 47.5% (fair +110). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -10791,17 +10791,17 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5112745098039215</v>
+        <v>0.4401</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-105</v>
+        <v>127</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -10825,7 +10825,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -105). Your call.</t>
+          <t>Model 44.0% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -10857,17 +10857,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.48875</v>
+        <v>0.5599000000000001</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>105</v>
+        <v>-127</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +105). Your call.</t>
+          <t>Model 56.0% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -10927,13 +10927,13 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.494356862745098</v>
+        <v>0.4982514563106796</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-104</v>
+        <v>-106</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -10957,7 +10957,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 49.4% (fair +102). Your call.</t>
+          <t>Model 49.8% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -10993,13 +10993,13 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5056218905472637</v>
+        <v>0.5017156862745098</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-102</v>
+        <v>-101</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -11023,7 +11023,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 50.6% (fair -102). Your call.</t>
+          <t>Model 50.2% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -11059,13 +11059,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4271555555555555</v>
+        <v>0.4430516431924883</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -11089,7 +11089,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 42.7% (fair +134). Your call.</t>
+          <t>Model 44.3% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11125,13 +11125,13 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5728504504504505</v>
+        <v>0.5569464454976303</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-134</v>
+        <v>-126</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-122</v>
+        <v>-111</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -11155,7 +11155,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 57.3% (fair -134). Your call.</t>
+          <t>Model 55.7% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11197,7 +11197,7 @@
         <v>104</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -11263,7 +11263,7 @@
         <v>-104</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -11329,7 +11329,7 @@
         <v>120</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -11395,7 +11395,7 @@
         <v>-120</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-126</v>
+        <v>176</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -11455,7 +11455,7 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4920192307692308</v>
+        <v>0.4935096153846154</v>
       </c>
       <c r="G27" s="14" t="n">
         <v>103</v>
@@ -11485,7 +11485,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 49.4% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -11521,13 +11521,13 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5080173913043478</v>
+        <v>0.506509756097561</v>
       </c>
       <c r="G28" s="14" t="n">
         <v>-103</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-107</v>
+        <v>-105</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -11551,7 +11551,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 50.7% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -11583,7 +11583,7 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
@@ -11593,7 +11593,7 @@
         <v>124</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="E30" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 8</t>
         </is>
       </c>
       <c r="F30" s="13" t="n">
@@ -11791,7 +11791,7 @@
         <v>-188</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -11857,7 +11857,7 @@
         <v>-113</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -11923,7 +11923,7 @@
         <v>113</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -11989,7 +11989,7 @@
         <v>116</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -12055,7 +12055,7 @@
         <v>-116</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -12121,7 +12121,7 @@
         <v>191</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -12187,7 +12187,7 @@
         <v>-191</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>-115</v>
+        <v>-121</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -12247,13 +12247,13 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.4249590163934426</v>
+        <v>0.4318067226890757</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -12277,7 +12277,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 42.5% (fair +135). Your call.</t>
+          <t>Model 43.2% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12313,13 +12313,13 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.5749991701244813</v>
+        <v>0.5682063829787234</v>
       </c>
       <c r="G40" s="14" t="n">
+        <v>-132</v>
+      </c>
+      <c r="H40" s="15" t="n">
         <v>-135</v>
-      </c>
-      <c r="H40" s="15" t="n">
-        <v>-141</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -12343,7 +12343,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 57.5% (fair -135). Your call.</t>
+          <t>Model 56.8% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -12375,17 +12375,17 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Over 10</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.3333</v>
+        <v>0.4017</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>200</v>
+        <v>149</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -12409,7 +12409,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 33.3% (fair +200). Your call.</t>
+          <t>Model 40.2% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -12441,17 +12441,17 @@
       </c>
       <c r="E42" s="20" t="inlineStr">
         <is>
-          <t>Under 10</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.6667000000000001</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-200</v>
+        <v>-149</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>-104</v>
+        <v>107</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -12475,7 +12475,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 66.7% (fair -200). Your call.</t>
+          <t>Model 59.8% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -12517,7 +12517,7 @@
         <v>142</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -12583,7 +12583,7 @@
         <v>-142</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>104</v>
+        <v>-105</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -12643,13 +12643,13 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.5218909090909091</v>
+        <v>0.5157883720930233</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>-109</v>
+        <v>-107</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>-120</v>
+        <v>-115</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -12673,7 +12673,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -12709,13 +12709,13 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.4781447963800905</v>
+        <v>0.4842396313364055</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -12739,7 +12739,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 48.4% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -12775,13 +12775,13 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.4482159624413146</v>
+        <v>0.3925</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>123</v>
+        <v>155</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -12805,7 +12805,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 44.8% (fair +123). Your call.</t>
+          <t>Model 39.2% (fair +155). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -12841,13 +12841,13 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5517878048780488</v>
+        <v>0.6074999999999999</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-123</v>
+        <v>-155</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>-105</v>
+        <v>108</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -12871,7 +12871,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 60.7% (fair -155). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -12907,10 +12907,10 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.381015625</v>
+        <v>0.3828515625</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H49" s="15" t="n">
         <v>156</v>
@@ -12937,7 +12937,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 38.1% (fair +162). Your call.</t>
+          <t>Model 38.3% (fair +161). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -12973,13 +12973,13 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.6189661596958175</v>
+        <v>0.6171798449612403</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-162</v>
+        <v>-161</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>-163</v>
+        <v>-158</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -13003,7 +13003,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 61.9% (fair -162). Your call.</t>
+          <t>Model 61.7% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -13035,7 +13035,7 @@
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F51" s="13" t="n">
@@ -13045,7 +13045,7 @@
         <v>115</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -13101,7 +13101,7 @@
       </c>
       <c r="E52" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F52" s="13" t="n">
@@ -13111,7 +13111,7 @@
         <v>-115</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -13171,13 +13171,13 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.4612000000000001</v>
+        <v>0.4955</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -13201,7 +13201,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -13237,13 +13237,13 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.538826872246696</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-117</v>
+        <v>-102</v>
       </c>
       <c r="H54" s="15" t="n">
-        <v>-127</v>
+        <v>110</v>
       </c>
       <c r="I54" s="13">
         <f>IF($H$54="","",IF($H$54&lt;0,-$H$54/(-$H$54+100),100/($H$54+100)))</f>
@@ -13267,7 +13267,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 50.4% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -13303,10 +13303,10 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.4234873949579832</v>
+        <v>0.4221008403361344</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H55" s="15" t="n">
         <v>138</v>
@@ -13333,7 +13333,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 42.3% (fair +136). Your call.</t>
+          <t>Model 42.2% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -13369,13 +13369,13 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.5764689075630252</v>
+        <v>0.5779244813278008</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>-136</v>
+        <v>-137</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>-138</v>
+        <v>-141</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -13399,7 +13399,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -13441,7 +13441,7 @@
         <v>336</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -13507,7 +13507,7 @@
         <v>-336</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>-101</v>
+        <v>106</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -13567,13 +13567,13 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.4289270386266094</v>
+        <v>0.4285</v>
       </c>
       <c r="G59" s="14" t="n">
         <v>133</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -13633,13 +13633,13 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.5710437768240343</v>
+        <v>0.5715</v>
       </c>
       <c r="G60" s="14" t="n">
         <v>-133</v>
       </c>
       <c r="H60" s="15" t="n">
-        <v>-133</v>
+        <v>-101</v>
       </c>
       <c r="I60" s="13">
         <f>IF($H$60="","",IF($H$60&lt;0,-$H$60/(-$H$60+100),100/($H$60+100)))</f>
@@ -14339,10 +14339,10 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.4761290322580645</v>
+        <v>0.4732258064516129</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H71" s="15" t="n">
         <v>117</v>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 47.3% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -14405,13 +14405,13 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.5238855855855856</v>
+        <v>0.5267422907488987</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>-110</v>
+        <v>-111</v>
       </c>
       <c r="H72" s="15" t="n">
-        <v>-122</v>
+        <v>-127</v>
       </c>
       <c r="I72" s="13">
         <f>IF($H$72="","",IF($H$72&lt;0,-$H$72/(-$H$72+100),100/($H$72+100)))</f>
@@ -14435,7 +14435,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 52.7% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -14609,7 +14609,7 @@
         <v>109</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -14867,13 +14867,13 @@
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.4883173076923077</v>
+        <v>0.4845070422535211</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -14897,7 +14897,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -14933,10 +14933,10 @@
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.51165</v>
+        <v>0.5154923076923077</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>-105</v>
+        <v>-106</v>
       </c>
       <c r="H80" s="15" t="n">
         <v>-108</v>
@@ -14963,7 +14963,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -14999,10 +14999,10 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.5208</v>
+        <v>0.5072549019607843</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>-109</v>
+        <v>-103</v>
       </c>
       <c r="H81" s="15" t="n">
         <v>104</v>
@@ -15029,7 +15029,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 50.7% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -15065,13 +15065,13 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.4793</v>
+        <v>0.4927450980392157</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -15095,7 +15095,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 49.3% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -15131,10 +15131,10 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.465726872246696</v>
+        <v>0.4685903083700441</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H83" s="15" t="n">
         <v>127</v>
@@ -15161,7 +15161,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 46.9% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -15197,13 +15197,13 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.534295154185022</v>
+        <v>0.5314144144144144</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>-115</v>
+        <v>-113</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>-127</v>
+        <v>-122</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -15227,7 +15227,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -115). Your call.</t>
+          <t>Model 53.1% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -15395,10 +15395,10 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.5016</v>
+        <v>0.5363603603603604</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>-101</v>
+        <v>-116</v>
       </c>
       <c r="H87" s="15" t="n">
         <v>-122</v>
@@ -15425,7 +15425,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 50.2% (fair -101). Your call.</t>
+          <t>Model 53.6% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -15461,13 +15461,13 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.4984</v>
+        <v>0.4636563876651982</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -15491,7 +15491,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 46.4% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -17897,7 +17897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:Q75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17914,328 +17914,174 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="29" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="29" t="inlineStr">
         <is>
           <t>Texas Rangers offense vs Cleveland Guardians defense</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="30" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B60" s="30" t="inlineStr">
+      <c r="B62" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C60" s="30" t="inlineStr">
+      <c r="C62" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D60" s="30" t="inlineStr">
+      <c r="D62" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E60" s="30" t="inlineStr">
+      <c r="E62" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F60" s="30" t="inlineStr">
+      <c r="F62" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G60" s="30" t="inlineStr">
+      <c r="G62" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H60" s="30" t="inlineStr">
+      <c r="H62" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I60" s="30" t="inlineStr">
+      <c r="I62" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J60" s="30" t="inlineStr">
+      <c r="J62" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K60" s="30" t="inlineStr">
+      <c r="K62" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L60" s="30" t="inlineStr">
+      <c r="L62" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M60" s="30" t="inlineStr">
+      <c r="M62" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N60" s="30" t="inlineStr">
+      <c r="N62" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O60" s="30" t="inlineStr">
+      <c r="O62" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P60" s="30" t="inlineStr">
+      <c r="P62" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q60" s="30" t="inlineStr">
+      <c r="Q62" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B61" s="32" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="C61" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="D61" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E61" s="32" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="F61" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G61" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H61" s="33" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I61" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J61" s="36" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="K61" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="L61" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="M61" s="32" t="n">
-        <v>3.733</v>
-      </c>
-      <c r="N61" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O61" s="32" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="P61" s="32" t="n">
-        <v>4.133</v>
-      </c>
-      <c r="Q61" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B62" s="32" t="n">
-        <v>7.816</v>
-      </c>
-      <c r="C62" s="32" t="n">
-        <v>9.167</v>
-      </c>
-      <c r="D62" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E62" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F62" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G62" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H62" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I62" s="32" t="inlineStr"/>
-      <c r="J62" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K62" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L62" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M62" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N62" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O62" s="32" t="n">
-        <v>10.429</v>
-      </c>
-      <c r="P62" s="32" t="n">
-        <v>7.939</v>
-      </c>
-      <c r="Q62" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B63" s="32" t="n">
-        <v>1.041</v>
+        <v>4.15</v>
       </c>
       <c r="C63" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D63" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E63" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F63" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G63" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H63" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I63" s="32" t="inlineStr"/>
-      <c r="J63" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K63" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L63" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M63" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N63" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O63" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P63" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.4</v>
+      </c>
+      <c r="D63" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E63" s="32" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="F63" s="32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G63" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H63" s="33" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="I63" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J63" s="36" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="K63" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="L63" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="M63" s="32" t="n">
+        <v>3.733</v>
+      </c>
+      <c r="N63" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O63" s="32" t="n">
+        <v>4.533</v>
+      </c>
+      <c r="P63" s="32" t="n">
+        <v>4.133</v>
       </c>
       <c r="Q63" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B64" s="32" t="n">
-        <v>8.592000000000001</v>
+        <v>7.816</v>
       </c>
       <c r="C64" s="32" t="n">
-        <v>8.833</v>
+        <v>9.167</v>
       </c>
       <c r="D64" s="32" t="inlineStr">
         <is>
@@ -18289,398 +18135,398 @@
         </is>
       </c>
       <c r="O64" s="32" t="n">
-        <v>9</v>
+        <v>10.429</v>
       </c>
       <c r="P64" s="32" t="n">
-        <v>9.388</v>
+        <v>7.939</v>
       </c>
       <c r="Q64" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B65" s="32" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="C65" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H65" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I65" s="32" t="inlineStr"/>
+      <c r="J65" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q65" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B66" s="32" t="n">
+        <v>8.592000000000001</v>
+      </c>
+      <c r="C66" s="32" t="n">
+        <v>8.833</v>
+      </c>
+      <c r="D66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H66" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I66" s="32" t="inlineStr"/>
+      <c r="J66" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O66" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="P66" s="32" t="n">
+        <v>9.388</v>
+      </c>
+      <c r="Q66" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B65" s="32" t="n">
+      <c r="B67" s="32" t="n">
         <v>0.63</v>
       </c>
-      <c r="C65" s="32" t="n">
+      <c r="C67" s="32" t="n">
         <v>0.867</v>
       </c>
-      <c r="D65" s="32" t="n">
+      <c r="D67" s="32" t="n">
         <v>0.75</v>
       </c>
-      <c r="E65" s="32" t="n">
+      <c r="E67" s="32" t="n">
         <v>0.867</v>
       </c>
-      <c r="F65" s="32" t="n">
+      <c r="F67" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="G65" s="32" t="n">
+      <c r="G67" s="32" t="n">
         <v>1.2</v>
       </c>
-      <c r="H65" s="33" t="inlineStr">
+      <c r="H67" s="33" t="inlineStr">
         <is>
           <t>3rd</t>
         </is>
       </c>
-      <c r="I65" s="32" t="inlineStr">
+      <c r="I67" s="32" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="J65" s="33" t="inlineStr">
+      <c r="J67" s="33" t="inlineStr">
         <is>
           <t>8th</t>
         </is>
       </c>
-      <c r="K65" s="32" t="n">
+      <c r="K67" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L65" s="32" t="n">
+      <c r="L67" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="M65" s="32" t="n">
+      <c r="M67" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="N65" s="32" t="n">
+      <c r="N67" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="O65" s="32" t="n">
+      <c r="O67" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="P65" s="32" t="n">
+      <c r="P67" s="32" t="n">
         <v>0.375</v>
       </c>
-      <c r="Q65" s="35" t="inlineStr">
+      <c r="Q67" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="29" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>Cleveland Guardians offense vs Texas Rangers defense</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="30" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B68" s="30" t="inlineStr">
+      <c r="B70" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C68" s="30" t="inlineStr">
+      <c r="C70" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D68" s="30" t="inlineStr">
+      <c r="D70" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E68" s="30" t="inlineStr">
+      <c r="E70" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F68" s="30" t="inlineStr">
+      <c r="F70" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G68" s="30" t="inlineStr">
+      <c r="G70" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H68" s="30" t="inlineStr">
+      <c r="H70" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I68" s="30" t="inlineStr">
+      <c r="I70" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J68" s="30" t="inlineStr">
+      <c r="J70" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K68" s="30" t="inlineStr">
+      <c r="K70" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L68" s="30" t="inlineStr">
+      <c r="L70" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M68" s="30" t="inlineStr">
+      <c r="M70" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N68" s="30" t="inlineStr">
+      <c r="N70" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O68" s="30" t="inlineStr">
+      <c r="O70" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P68" s="30" t="inlineStr">
+      <c r="P70" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q68" s="30" t="inlineStr">
+      <c r="Q70" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E69" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="F69" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G69" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H69" s="34" t="inlineStr">
-        <is>
-          <t>22nd</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="33" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L69" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="M69" s="32" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="N69" s="32" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="P69" s="32" t="n">
-        <v>4.138</v>
-      </c>
-      <c r="Q69" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B70" s="32" t="n">
-        <v>7.735</v>
-      </c>
-      <c r="C70" s="32" t="n">
-        <v>9.143000000000001</v>
-      </c>
-      <c r="D70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O70" s="32" t="n">
-        <v>8.167</v>
-      </c>
-      <c r="P70" s="32" t="n">
-        <v>7.673</v>
-      </c>
-      <c r="Q70" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>0.959</v>
+        <v>3.88</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="D71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>3.4</v>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>22nd</t>
         </is>
       </c>
       <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J71" s="33" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L71" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="M71" s="32" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="N71" s="32" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>4.533</v>
+      </c>
+      <c r="P71" s="32" t="n">
+        <v>4.138</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>8</v>
+        <v>7.735</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>9.429</v>
+        <v>9.143000000000001</v>
       </c>
       <c r="D72" s="32" t="inlineStr">
         <is>
@@ -18734,71 +18580,225 @@
         </is>
       </c>
       <c r="O72" s="32" t="n">
-        <v>9.167</v>
+        <v>8.167</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>8.571</v>
+        <v>7.673</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q73" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B74" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C74" s="32" t="n">
+        <v>9.429</v>
+      </c>
+      <c r="D74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="32" t="n">
+        <v>9.167</v>
+      </c>
+      <c r="P74" s="32" t="n">
+        <v>8.571</v>
+      </c>
+      <c r="Q74" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B73" s="32" t="n">
+      <c r="B75" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="C73" s="32" t="n">
+      <c r="C75" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="D73" s="32" t="n">
+      <c r="D75" s="32" t="n">
         <v>0.15</v>
       </c>
-      <c r="E73" s="32" t="n">
+      <c r="E75" s="32" t="n">
         <v>0.133</v>
       </c>
-      <c r="F73" s="32" t="n">
+      <c r="F75" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="G73" s="32" t="n">
+      <c r="G75" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="H73" s="36" t="inlineStr">
+      <c r="H75" s="36" t="inlineStr">
         <is>
           <t>19th</t>
         </is>
       </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="33" t="inlineStr">
+      <c r="I75" s="32" t="inlineStr"/>
+      <c r="J75" s="33" t="inlineStr">
         <is>
           <t>5th</t>
         </is>
       </c>
-      <c r="K73" s="32" t="n">
+      <c r="K75" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L73" s="32" t="n">
+      <c r="L75" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="M73" s="32" t="n">
+      <c r="M75" s="32" t="n">
         <v>0.9330000000000001</v>
       </c>
-      <c r="N73" s="32" t="n">
+      <c r="N75" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="O73" s="32" t="n">
+      <c r="O75" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="P73" s="32" t="n">
+      <c r="P75" s="32" t="n">
         <v>0.781</v>
       </c>
-      <c r="Q73" s="35" t="inlineStr">
+      <c r="Q75" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
